--- a/examples/demo/public/samples/pivot.xlsx
+++ b/examples/demo/public/samples/pivot.xlsx
@@ -59,13 +59,13 @@
     <t>Units by region (pivot table)</t>
   </si>
   <si>
+    <t>Edit the Data sheet and the pivot table follows; right-click it and choose Show Field List to change its fields.</t>
+  </si>
+  <si>
     <t>Row Labels</t>
   </si>
   <si>
     <t>Sum of Units</t>
-  </si>
-  <si>
-    <t>Edit units on the Data sheet; the pivot refreshes when the file is opened in Excel.</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -2385,19 +2385,21 @@
     <col min="2" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
         <v>16</v>
       </c>
     </row>
